--- a/cases/Case_14bus_v2/pf_info_extendedCase_14bus_v2.xlsx
+++ b/cases/Case_14bus_v2/pf_info_extendedCase_14bus_v2.xlsx
@@ -37,124 +37,124 @@
     <t>Qg</t>
   </si>
   <si>
-    <t>1.15839567121002</t>
-  </si>
-  <si>
-    <t>0.388349398724110</t>
-  </si>
-  <si>
-    <t>0.396039600584542</t>
-  </si>
-  <si>
-    <t>0.291262146856676</t>
-  </si>
-  <si>
-    <t>0.339805832431900</t>
-  </si>
-  <si>
-    <t>0.205123770498175</t>
-  </si>
-  <si>
-    <t>0.0253720081939931</t>
-  </si>
-  <si>
-    <t>0.0251354922359287</t>
-  </si>
-  <si>
-    <t>0.104141715999112</t>
-  </si>
-  <si>
-    <t>0.141727680442046</t>
-  </si>
-  <si>
-    <t>0.248136922140451</t>
-  </si>
-  <si>
-    <t>-0.450139329719664</t>
-  </si>
-  <si>
-    <t>-0.190377450569369</t>
-  </si>
-  <si>
-    <t>-0.793669443384482</t>
-  </si>
-  <si>
-    <t>-0.213168422305495</t>
-  </si>
-  <si>
-    <t>-2.41120023173841e-9</t>
-  </si>
-  <si>
-    <t>9.77608135171822e-9</t>
-  </si>
-  <si>
-    <t>3.42083882666426e-9</t>
-  </si>
-  <si>
-    <t>3.81491298308853e-8</t>
-  </si>
-  <si>
-    <t>1.31439878717635e-8</t>
-  </si>
-  <si>
-    <t>1.19314754134632</t>
-  </si>
-  <si>
-    <t>0.399999880685833</t>
-  </si>
-  <si>
-    <t>0.399999996590387</t>
-  </si>
-  <si>
-    <t>0.300000011262377</t>
-  </si>
-  <si>
-    <t>0.350000007404857</t>
-  </si>
-  <si>
-    <t>0.200000008055732</t>
-  </si>
-  <si>
-    <t>0.0249999952791862</t>
-  </si>
-  <si>
-    <t>0.0249999995544679</t>
-  </si>
-  <si>
-    <t>0.0999999612913256</t>
-  </si>
-  <si>
-    <t>0.129059021445532</t>
-  </si>
-  <si>
-    <t>0.586490448119801</t>
-  </si>
-  <si>
-    <t>0.675707912601161</t>
-  </si>
-  <si>
-    <t>0.308135788424937</t>
-  </si>
-  <si>
-    <t>1.24632642081829</t>
-  </si>
-  <si>
-    <t>0.316108742988430</t>
-  </si>
-  <si>
-    <t>0.00126227518767278</t>
-  </si>
-  <si>
-    <t>1.93025312527237e-5</t>
-  </si>
-  <si>
-    <t>1.89503866994520e-5</t>
-  </si>
-  <si>
-    <t>0.000325328278412454</t>
-  </si>
-  <si>
-    <t>0.000602590093022607</t>
+    <t>1.18982351776559</t>
+  </si>
+  <si>
+    <t>0.388349395287863</t>
+  </si>
+  <si>
+    <t>0.396039600545935</t>
+  </si>
+  <si>
+    <t>0.291262146967627</t>
+  </si>
+  <si>
+    <t>0.339805832330305</t>
+  </si>
+  <si>
+    <t>0.205286281633235</t>
+  </si>
+  <si>
+    <t>-0.00508366516260694</t>
+  </si>
+  <si>
+    <t>0.0251363928864405</t>
+  </si>
+  <si>
+    <t>0.104147465626575</t>
+  </si>
+  <si>
+    <t>0.141765955181269</t>
+  </si>
+  <si>
+    <t>0.253015816777368</t>
+  </si>
+  <si>
+    <t>-0.458296126289061</t>
+  </si>
+  <si>
+    <t>-0.192890225067323</t>
+  </si>
+  <si>
+    <t>-0.799451264093259</t>
+  </si>
+  <si>
+    <t>-0.214958022394270</t>
+  </si>
+  <si>
+    <t>-1.87805430825782e-9</t>
+  </si>
+  <si>
+    <t>1.04965373217728e-8</t>
+  </si>
+  <si>
+    <t>3.41900166093551e-9</t>
+  </si>
+  <si>
+    <t>3.81847400798124e-8</t>
+  </si>
+  <si>
+    <t>1.31421169444352e-8</t>
+  </si>
+  <si>
+    <t>1.22551822329856</t>
+  </si>
+  <si>
+    <t>0.399999877146499</t>
+  </si>
+  <si>
+    <t>0.399999996551394</t>
+  </si>
+  <si>
+    <t>0.300000011376656</t>
+  </si>
+  <si>
+    <t>0.350000007300214</t>
+  </si>
+  <si>
+    <t>0.200000006961828</t>
+  </si>
+  <si>
+    <t>-0.00500000656986654</t>
+  </si>
+  <si>
+    <t>0.0249999995579531</t>
+  </si>
+  <si>
+    <t>0.0999999613313753</t>
+  </si>
+  <si>
+    <t>0.129059021435767</t>
+  </si>
+  <si>
+    <t>0.627211912899869</t>
+  </si>
+  <si>
+    <t>0.688555365392938</t>
+  </si>
+  <si>
+    <t>0.311251529794260</t>
+  </si>
+  <si>
+    <t>1.25780837916596</t>
+  </si>
+  <si>
+    <t>0.318411736112506</t>
+  </si>
+  <si>
+    <t>0.00126427555249701</t>
+  </si>
+  <si>
+    <t>7.64985741979068e-7</t>
+  </si>
+  <si>
+    <t>1.89517469705312e-5</t>
+  </si>
+  <si>
+    <t>0.000325364173798603</t>
+  </si>
+  <si>
+    <t>0.000602915617306556</t>
   </si>
 </sst>
 </file>
@@ -546,7 +546,7 @@
         <v>1.03</v>
       </c>
       <c r="C2">
-        <v>1.579513746415983E-16</v>
+        <v>1.670418904637509E-16</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -555,10 +555,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.225518223298555</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>-0.2606062912806886</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -569,7 +569,7 @@
         <v>1.03</v>
       </c>
       <c r="C3">
-        <v>-0.04525370883924262</v>
+        <v>-0.04651415196203403</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -578,10 +578,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>0.3999998771464987</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.4720450100777331</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -592,7 +592,7 @@
         <v>1.01</v>
       </c>
       <c r="C4">
-        <v>-0.08496263997583167</v>
+        <v>-0.08703660390633892</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -601,10 +601,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>0.3999999965513941</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.194819127317996</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -612,10 +612,10 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.9993857339846809</v>
+        <v>0.9988917002221633</v>
       </c>
       <c r="C5">
-        <v>-0.104083398095561</v>
+        <v>-0.1067518617762736</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -624,10 +624,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>-7.071588992157984E-08</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>-6.840050001399867E-08</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -635,10 +635,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.006113812417038</v>
+        <v>1.005594239924474</v>
       </c>
       <c r="C6">
-        <v>-0.09698166615960305</v>
+        <v>-0.09952080186882445</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -647,10 +647,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1.987268476166815E-08</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>4.797033613390678E-08</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -661,7 +661,7 @@
         <v>1.03</v>
       </c>
       <c r="C7">
-        <v>-0.2151738720070119</v>
+        <v>-0.2217321730629859</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -670,10 +670,10 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>0.3000000113766556</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.8234348020160567</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -681,10 +681,10 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.9942537894021076</v>
+        <v>0.9939391233147048</v>
       </c>
       <c r="C8">
-        <v>-0.1214317925431795</v>
+        <v>-0.126039810609252</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>8.329833711684387E-09</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2.345160510230926E-08</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -707,7 +707,7 @@
         <v>1.03</v>
       </c>
       <c r="C9">
-        <v>-0.06119263196891782</v>
+        <v>-0.06578155613395506</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -716,10 +716,10 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>0.3500000073002139</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.2214067630660983</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -727,10 +727,10 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.9716542999096324</v>
+        <v>0.9713084496386745</v>
       </c>
       <c r="C10">
-        <v>-0.1706938062007487</v>
+        <v>-0.1763777964017369</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -739,10 +739,10 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>-1.177619418646358E-08</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>-5.630269309109259E-08</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -750,10 +750,10 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.9750211180791037</v>
+        <v>0.9742492550922061</v>
       </c>
       <c r="C11">
-        <v>-0.1706947015053131</v>
+        <v>-0.1776002318955821</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -762,10 +762,10 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>0.2000000069618283</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1.82969301515401E-09</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -773,10 +773,10 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.9853376637764527</v>
+        <v>0.983543646155976</v>
       </c>
       <c r="C12">
-        <v>-0.1979901473440626</v>
+        <v>-0.2077122419649518</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -785,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>-0.005000006569866544</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>-1.032380259058385E-08</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -796,10 +796,10 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.9946095075366331</v>
+        <v>0.9945738702802914</v>
       </c>
       <c r="C13">
-        <v>-0.2437348388486146</v>
+        <v>-0.250246908317458</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -808,10 +808,10 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>0.02499999955795312</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>-3.400449713475417E-09</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -819,10 +819,10 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.9602296287510631</v>
+        <v>0.9601766181227075</v>
       </c>
       <c r="C14">
-        <v>-0.255229436265854</v>
+        <v>-0.2616785350407841</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -831,10 +831,10 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>0.09999996133137534</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>-3.66640945936858E-08</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -842,10 +842,10 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.9106126696140026</v>
+        <v>0.910366817412159</v>
       </c>
       <c r="C15">
-        <v>-0.2375764512905657</v>
+        <v>-0.2436115958364653</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -854,10 +854,10 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>0.1290590214357669</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>-1.196414717297145E-08</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -865,10 +865,10 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>1.122250262191585</v>
+        <v>1.131752346130331</v>
       </c>
       <c r="C16">
-        <v>0.6678824129160525</v>
+        <v>0.6825663930086111</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -888,10 +888,10 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>1.320799323639836</v>
+        <v>1.325616922524152</v>
       </c>
       <c r="C17">
-        <v>0.1320900571054738</v>
+        <v>0.1301782991883657</v>
       </c>
       <c r="D17" t="s">
         <v>8</v>
@@ -911,10 +911,10 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1.149064927712964</v>
+        <v>1.150540044617028</v>
       </c>
       <c r="C18">
-        <v>0.1233379306807202</v>
+        <v>0.120992979811249</v>
       </c>
       <c r="D18" t="s">
         <v>9</v>
@@ -934,10 +934,10 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>1.516305895425651</v>
+        <v>1.519751923410268</v>
       </c>
       <c r="C19">
-        <v>-0.09966518484903066</v>
+        <v>-0.1064865681718771</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
@@ -957,10 +957,10 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>1.175713966395676</v>
+        <v>1.176771472932261</v>
       </c>
       <c r="C20">
-        <v>0.1131009859919058</v>
+        <v>0.1083538293395228</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -980,10 +980,10 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.9750405371195523</v>
+        <v>0.9742687203072794</v>
       </c>
       <c r="C21">
-        <v>-0.164383421375332</v>
+        <v>-0.1712789476999418</v>
       </c>
       <c r="D21" t="s">
         <v>12</v>
@@ -1003,10 +1003,10 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.9853379574762119</v>
+        <v>0.9835436576653066</v>
       </c>
       <c r="C22">
-        <v>-0.1972176607918635</v>
+        <v>-0.2078673036689248</v>
       </c>
       <c r="D22" t="s">
         <v>13</v>
@@ -1026,10 +1026,10 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.9946097932816633</v>
+        <v>0.9945741560561051</v>
       </c>
       <c r="C23">
-        <v>-0.2429766874163544</v>
+        <v>-0.2494887025524549</v>
       </c>
       <c r="D23" t="s">
         <v>14</v>
@@ -1049,10 +1049,10 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.9602347102041245</v>
+        <v>0.9601817004165675</v>
       </c>
       <c r="C24">
-        <v>-0.2519757973803949</v>
+        <v>-0.2584245368847291</v>
       </c>
       <c r="D24" t="s">
         <v>15</v>
@@ -1072,10 +1072,10 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.9106225954835839</v>
+        <v>0.9103767513259211</v>
       </c>
       <c r="C25">
-        <v>-0.2329072877056984</v>
+        <v>-0.2389399100544596</v>
       </c>
       <c r="D25" t="s">
         <v>16</v>
